--- a/auto_gen/src/main/resources/luban/Datas/function/function.xlsx
+++ b/auto_gen/src/main/resources/luban/Datas/function/function.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="26">
   <si>
     <t>##var</t>
   </si>
@@ -50,6 +50,9 @@
     <t>close</t>
   </si>
   <si>
+    <t>sort</t>
+  </si>
+  <si>
     <t>extra_info</t>
   </si>
   <si>
@@ -90,6 +93,9 @@
   </si>
   <si>
     <t>是否关闭（总开关）</t>
+  </si>
+  <si>
+    <t>排序</t>
   </si>
   <si>
     <t>功能额外信息</t>
@@ -1037,17 +1043,17 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:H6"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelRow="5" outlineLevelCol="7"/>
+  <dimension ref="A1:I6"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelRow="5"/>
   <cols>
     <col min="4" max="4" width="18.275" customWidth="1"/>
     <col min="5" max="5" width="22.4916666666667" customWidth="1"/>
     <col min="6" max="6" width="14.3916666666667" customWidth="1"/>
     <col min="7" max="7" width="18.3583333333333" customWidth="1"/>
-    <col min="8" max="8" width="20.9416666666667" customWidth="1"/>
+    <col min="8" max="9" width="20.9416666666667" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8">
+    <row r="1" spans="1:9">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1072,86 +1078,98 @@
       <c r="H1" t="s">
         <v>7</v>
       </c>
+      <c r="I1" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="2" spans="1:8">
+    <row r="2" spans="1:9">
       <c r="A2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="H2" t="s">
         <v>10</v>
       </c>
+      <c r="I2" t="s">
+        <v>11</v>
+      </c>
     </row>
-    <row r="3" spans="1:8">
+    <row r="3" spans="1:9">
       <c r="A3" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H3" t="s">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="I3" t="s">
+        <v>14</v>
       </c>
     </row>
-    <row r="4" spans="1:8">
+    <row r="4" spans="1:9">
       <c r="A4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B4" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C4" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D4" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E4" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F4" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G4" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H4" t="s">
-        <v>21</v>
+        <v>22</v>
+      </c>
+      <c r="I4" t="s">
+        <v>23</v>
       </c>
     </row>
-    <row r="5" spans="1:8">
+    <row r="5" spans="1:9">
       <c r="B5">
         <v>0</v>
       </c>
@@ -1159,16 +1177,19 @@
         <v>-1</v>
       </c>
       <c r="D5" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="E5" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="G5" t="b">
         <v>0</v>
       </c>
+      <c r="H5">
+        <v>0</v>
+      </c>
     </row>
-    <row r="6" spans="1:8">
+    <row r="6" spans="1:9">
       <c r="B6">
         <v>1</v>
       </c>
@@ -1176,10 +1197,10 @@
         <v>0</v>
       </c>
       <c r="D6" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="E6" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="G6">
         <v>0</v>
